--- a/product_selector_out/STM32F301.xlsx
+++ b/product_selector_out/STM32F301.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>8, 9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>8, 9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
@@ -3643,14 +3643,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
@@ -3673,9 +3673,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="6" t="inlineStr">
@@ -3728,9 +3728,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM12" s="9" t="inlineStr">
@@ -3970,14 +3970,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -4000,9 +4000,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="6" t="inlineStr">
@@ -4055,9 +4055,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="9" t="inlineStr">
@@ -4297,14 +4297,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -4327,9 +4327,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="6" t="inlineStr">
@@ -4342,9 +4342,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE14" s="9" t="inlineStr">
@@ -4382,9 +4382,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM14" s="9" t="inlineStr">
@@ -4624,14 +4624,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -4654,9 +4654,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="6" t="inlineStr">
@@ -4709,9 +4709,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM15" s="9" t="inlineStr">
@@ -4951,14 +4951,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -4981,9 +4981,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="6" t="inlineStr">
@@ -5036,9 +5036,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM16" s="9" t="inlineStr">
@@ -5278,14 +5278,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -5308,9 +5308,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="6" t="inlineStr">
@@ -5323,9 +5323,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE17" s="9" t="inlineStr">
@@ -5363,9 +5363,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM17" s="9" t="inlineStr">

--- a/product_selector_out/STM32F301.xlsx
+++ b/product_selector_out/STM32F301.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
@@ -2955,12 +2987,17 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f301c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -2981,16 +3018,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3003,6 +3038,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3022,7 +3058,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3045,7 +3083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM17"/>
+  <dimension ref="A1:BN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3113,6 +3151,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3446,6 +3485,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -3541,6 +3585,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -3863,7 +3908,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4190,7 +4240,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4517,7 +4572,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4844,7 +4904,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5171,7 +5236,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5498,7 +5568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5506,8 +5581,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
